--- a/daily_matches/job_matches_2026-03-25.xlsx
+++ b/daily_matches/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,130 +468,130 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GenAI and Agentic AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Cortex, TensorFlow, PyTorch, Keras, Azure ML</t>
+          <t>Generative AI, RAG, S3, Glue, Athena, Redshift, Data Lake, Jenkins, Git, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10a9b25c91a6cdc7</t>
+          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Machine Learning &amp; AI Engineer - ITS4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LightEdge</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Copilot, Prompt Engineering, Data Lake, MLflow</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, AWS SageMaker, S3, Glue, Athena, Redshift, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bb7334f3f2d66e8</t>
+          <t>https://www.indeed.com/viewjob?jk=2c23f8b8c5caacd8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Data Platform Engineer</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Dataflow, Docker, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Snowflake, NoSQL</t>
+          <t>Data Scientist, Redshift, BigQuery, MLflow, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=815d21355bca9afb</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Distinguished Architect, Data Platform</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CloudZero</t>
+          <t>Expertshub</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Kinesis, Snowflake, BigQuery, Redshift, Kafka, SQL, R</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd1095da2d18982</t>
+          <t>https://www.indeed.com/viewjob?jk=bf7747fc231cb803</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer, Storage Engineering</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Intercontinental Exchange</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, NoSQL, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Tableau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b976b4aa36a92b0</t>
+          <t>https://www.indeed.com/viewjob?jk=f47fe1b011621142</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Frontend Engineer (Angular) – Healthcare SaaS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fusion Academy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Azure ML, Data Lake, CI/CD, Git, Databricks, Kafka, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02d8ce8f0c1066e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Apache Airflow, CI/CD, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,182 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0896fe674cad86</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, Snowflake, Python, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=abd524b0dff0e60e</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Analytics Engineer II</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Mercury Insurance Company</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Redshift, BigQuery, FastAPI, Snowflake, BigQuery, Redshift, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba12e07905b7df00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Lion Holdings</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Valuetainment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, SQL, R</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6dae9d085413832c</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Developer I</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Western &amp; Southern Financial Group</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d098467416c839b6</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>West Monroe</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, Snowflake, Databricks, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73d9a0e0a8dbd3ec</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-25.xlsx
+++ b/daily_matches/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior BackEnd Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, Glue, Athena, Redshift, Data Lake, Jenkins, Git, Databricks</t>
+          <t>LangChain, RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=933ad44aa47970a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b5da0b19b9bea7fb</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; AI Engineer - ITS4</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, RAG, AWS SageMaker, S3, Glue, Athena, Redshift, Redshift</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, MLflow, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c23f8b8c5caacd8</t>
+          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr Data Scientist</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BECU</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tukwila, WA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, MLflow, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,89 +566,89 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad58dde8c86078b</t>
+          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Database Administrator / Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Expertshub</t>
+          <t>Clear Channel Outdoor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Docker</t>
+          <t>RAG, S3, Glue, Redshift, CI/CD, Git, Redshift, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf7747fc231cb803</t>
+          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer, Storage Engineering</t>
+          <t>Gen AI Product Owner</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Intercontinental Exchange</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Tableau</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Cortex, Git, Snowflake, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f47fe1b011621142</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c0abd96c7dc025</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fusion Academy</t>
+          <t>Polaris I/O</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Azure ML, Data Lake, CI/CD, Git, Databricks, Kafka, Power BI, Python</t>
+          <t>RAG, S3, FastAPI, Kubernetes, Git, PostgreSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c239fde5950cdb3c</t>
+          <t>https://www.indeed.com/viewjob?jk=f266e67ee961e84e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Applied AI &amp; Analytics Associate - Office of the CEO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>SharkNinja</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, Apache Airflow, CI/CD, Git, Databricks, Python</t>
+          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,129 +706,129 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef1d9dc4f2a3c77</t>
+          <t>https://www.indeed.com/viewjob?jk=5a522d2cf1dfe88a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Engineer 3- Onsite 4 Days X Week in Philadelphia</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, Snowflake, Python, R</t>
+          <t>RAG, S3, Redshift, Data Lake, Kubernetes, Git, Databricks, Redshift, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd524b0dff0e60e</t>
+          <t>https://www.indeed.com/viewjob?jk=6ae523531d4ed7ee</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>k1x</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Redshift, BigQuery, FastAPI, Snowflake, BigQuery, Redshift, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba12e07905b7df00</t>
+          <t>https://www.indeed.com/viewjob?jk=01f0d263a7a4c743</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Lion Holdings</t>
+          <t>RESEARCH SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Valuetainment</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, SQL, R</t>
+          <t>Data Scientist, Docker, Git, Snowflake, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dae9d085413832c</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e4f1f2307507c5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Developer I</t>
+          <t>APPLICATION ENGINEER II</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Western &amp; Southern Financial Group</t>
+          <t>Moffitt Cancer Center</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, Python, SQL, R, Java</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d098467416c839b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a2ff2a81057f89ab</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer</t>
+          <t>Software Engineer 1 - BE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Snowflake, Databricks, PostgreSQL, Python, SQL, R</t>
+          <t>CI/CD, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,147 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d9a0e0a8dbd3ec</t>
+          <t>https://www.indeed.com/viewjob?jk=54f0415f2cc4a7fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Agentic) – AI &amp; Workflow Automation</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CloudBees Inc</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Lewes, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LangChain, Gemini, Prompt Engineering, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b1d2783522fc149</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer (People Tech, Intelligent Foundations &amp; Experiences)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbaf9e2cd1c3df20</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SoundThinking</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51d19b1a1f93d6ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Clinical Data Analyst Translational AI in Oncology</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Moffitt Cancer Center</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f85b9ce264b2c748</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-25.xlsx
+++ b/daily_matches/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior BackEnd Engineer</t>
+          <t>AI/ML Engineer - Local to Dallas who can attend Face to Face Interview</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Git, Kafka</t>
+          <t>AI Engineer, Data Scientist, RAG, Hugging Face, Pinecone, Prompt Engineering, S3, EC2, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5da0b19b9bea7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=a98548f3564e6736</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Automation Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, MLflow, Kubernetes</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=073969ba933b74ce</t>
+          <t>https://www.indeed.com/viewjob?jk=156fbc68878e6aa6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, Power BI, Python, SQL</t>
+          <t>Data Scientist, RAG, MLflow, Docker, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a60f5615bdba859</t>
+          <t>https://www.indeed.com/viewjob?jk=ce8a4999ff33c8c2</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer</t>
+          <t>Data Science Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Clear Channel Outdoor</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Redshift, CI/CD, Git, Redshift, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, MLflow, Docker, CI/CD, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e24a399eaddada3</t>
+          <t>https://www.indeed.com/viewjob?jk=7431618d3954e6cd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gen AI Product Owner</t>
+          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>HCM</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, Cortex, Git, Snowflake, R</t>
+          <t>RAG, CI/CD, GitHub Actions, Git, Databricks, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c0abd96c7dc025</t>
+          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Polaris I/O</t>
+          <t>Relias</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, FastAPI, Kubernetes, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Synapse, Data Lake, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,102 +671,102 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f266e67ee961e84e</t>
+          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Applied AI &amp; Analytics Associate - Office of the CEO</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SharkNinja</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Kafka, Hadoop, Cassandra, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a522d2cf1dfe88a</t>
+          <t>https://www.indeed.com/viewjob?jk=1b263e0344e64430</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer 3- Onsite 4 Days X Week in Philadelphia</t>
+          <t>Data Scientist 2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Data Lake, Kubernetes, Git, Databricks, Redshift, Python, R</t>
+          <t>Data Scientist, PyTorch, CI/CD, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ae523531d4ed7ee</t>
+          <t>https://www.indeed.com/viewjob?jk=0271b7b2098558eb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>k1x</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, PyTorch, CI/CD, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01f0d263a7a4c743</t>
+          <t>https://www.indeed.com/viewjob?jk=648587140f4c8181</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RESEARCH SOFTWARE ENGINEER</t>
+          <t>Data Engineer, Quantitative Research</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Moffitt Cancer Center</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Lone Tree, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Docker, Git, Snowflake, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, MLflow, CI/CD, Git, Polars, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,217 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e4f1f2307507c5</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>APPLICATION ENGINEER II</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Moffitt Cancer Center</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2ff2a81057f89ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Software Engineer 1 - BE</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CI/CD, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=54f0415f2cc4a7fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (Agentic) – AI &amp; Workflow Automation</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CloudBees Inc</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Lewes, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>LangChain, Gemini, Prompt Engineering, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1d2783522fc149</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer (People Tech, Intelligent Foundations &amp; Experiences)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>McLean, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cbaf9e2cd1c3df20</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sr. Software Engineer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>SoundThinking</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Fremont, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Kubernetes, CI/CD, Git, PostgreSQL, NoSQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51d19b1a1f93d6ca</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Clinical Data Analyst Translational AI in Oncology</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Moffitt Cancer Center</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Tampa, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f85b9ce264b2c748</t>
+          <t>https://www.indeed.com/viewjob?jk=31937d3ad5425679</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-25.xlsx
+++ b/daily_matches/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Local to Dallas who can attend Face to Face Interview</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>Blitzy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Hugging Face, Pinecone, Prompt Engineering, S3, EC2, FastAPI, Docker</t>
+          <t>Generative AI, AKS, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a98548f3564e6736</t>
+          <t>https://www.indeed.com/viewjob?jk=df4e6b9e9c01399c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Automation Engineer</t>
+          <t>AI-Driven Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, FAISS, Pinecone, TensorFlow, PyTorch, Docker, CI/CD, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156fbc68878e6aa6</t>
+          <t>https://www.indeed.com/viewjob?jk=99f9b4e746eac04a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Shell Energy Retail</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, Docker, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Keras, MLflow, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce8a4999ff33c8c2</t>
+          <t>https://www.indeed.com/viewjob?jk=b14fe0ff029bd2cd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Science Engineer</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Wichita, KS, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, MLflow, Docker, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7431618d3954e6cd</t>
+          <t>https://www.indeed.com/viewjob?jk=38f2f450ea0c5618</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Integration &amp; Analytics Platforms</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, MLflow, Hadoop, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3154ef15f06177d4</t>
+          <t>https://www.indeed.com/viewjob?jk=d677af7e8825b7c5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Sr. Software Engineer - AI Solutions</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Relias</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Synapse, Data Lake, CI/CD, Git, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Data Scientist, Generative AI, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a059dfc3b3900d0</t>
+          <t>https://www.indeed.com/viewjob?jk=892065aa8a5ffed7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Ai Vantage</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Vienna, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Kafka, Hadoop, Cassandra, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, FAISS, Pinecone, TensorFlow, PyTorch, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b263e0344e64430</t>
+          <t>https://www.indeed.com/viewjob?jk=27bcf72fc64343db</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Scientist 2</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, PyTorch, CI/CD, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0271b7b2098558eb</t>
+          <t>https://www.indeed.com/viewjob?jk=48ed466d6fbd359a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, PyTorch, CI/CD, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,42 +776,182 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=648587140f4c8181</t>
+          <t>https://www.indeed.com/viewjob?jk=dbfdd0d819992e3a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer, Quantitative Research</t>
+          <t>OpenAM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lone Tree, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Azure ML, Data Lake, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Java AI Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, MLflow, CI/CD, Git, Polars, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=31937d3ad5425679</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38ab9248ed029ab5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Computer Vision Developer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tommy Car Wash</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Holland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, OpenCV, Docker, CI/CD, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7748a3307d8c207a</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Machine Learning &amp; Computer Vision Developer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tommy Car Wash</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TensorFlow, PyTorch, OpenCV, Docker, CI/CD, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc861ec119fef406</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Citian</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Snowflake, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fa6cd3419de28e0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-25.xlsx
+++ b/daily_matches/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Data Scientist - Payments Optimization</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Blitzy</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, AKS, CI/CD, Jenkins, Terraform, Git, PostgreSQL, MongoDB, NoSQL, Python</t>
+          <t>Data Scientist, TensorFlow, CI/CD, Git, Snowflake, Databricks, PySpark, Hadoop, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df4e6b9e9c01399c</t>
+          <t>https://www.indeed.com/viewjob?jk=eb1f261a745afe34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI-Driven Threat Intelligence Analyst</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vivint</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, FAISS, Pinecone, TensorFlow, PyTorch, Docker, CI/CD, Python</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,369 +531,369 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f9b4e746eac04a</t>
+          <t>https://www.indeed.com/viewjob?jk=9a55821b896b85e9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Shell Energy Retail</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Keras, MLflow, Git, Python, R, Java</t>
+          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, Git, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b14fe0ff029bd2cd</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5c7581bcb185c7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38f2f450ea0c5618</t>
+          <t>https://www.indeed.com/viewjob?jk=27dbf7650e8555c5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, MLflow, Hadoop, Python, R</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d677af7e8825b7c5</t>
+          <t>https://www.indeed.com/viewjob?jk=2737000d1f54a3e9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Solutions</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, CI/CD, Git, Databricks, Python, SQL, R, Java</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=892065aa8a5ffed7</t>
+          <t>https://www.indeed.com/viewjob?jk=c086a116a8b60392</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, FAISS, Pinecone, TensorFlow, PyTorch, Git, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27bcf72fc64343db</t>
+          <t>https://www.indeed.com/viewjob?jk=9292b690258e6472</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, Git, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48ed466d6fbd359a</t>
+          <t>https://www.indeed.com/viewjob?jk=b43103393c0742b9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, Git, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbfdd0d819992e3a</t>
+          <t>https://www.indeed.com/viewjob?jk=3a9068b10718331e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OpenAM</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure ML, Data Lake, CI/CD, GitHub Actions, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b375c5df5a63eee</t>
+          <t>https://www.indeed.com/viewjob?jk=2ddb39444130c51a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java AI Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, CI/CD, GitHub Actions, Git, R, Java, Scala</t>
+          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, Git, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ab9248ed029ab5</t>
+          <t>https://www.indeed.com/viewjob?jk=e3019f34dbd3931a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Computer Vision Developer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Holland, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, OpenCV, Docker, CI/CD, Python, R, Java, Optimization</t>
+          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, Git, Kafka, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7748a3307d8c207a</t>
+          <t>https://www.indeed.com/viewjob?jk=fcd2280254ddc564</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning &amp; Computer Vision Developer</t>
+          <t>Solutions Engineer(Python/Airflow)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tommy Car Wash</t>
+          <t>EDB</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, OpenCV, Docker, CI/CD, Python, R, Java, Optimization</t>
+          <t>RAG, S3, EC2, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,952 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc861ec119fef406</t>
+          <t>https://www.indeed.com/viewjob?jk=f2e5544787ac4ad7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Citian</t>
+          <t>Al Warren Oil Company, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>Bensenville, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5503ca5f60f1076</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Al Warren Oil Company, Inc.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd4f51cd9252cb65</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Altom Transport, Inc.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Copilot, Docker, CI/CD, Jenkins, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5677557f087cb138</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>SoFi</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Keras, Snowflake, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b3e376a58c36142</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DIGITAL &amp; TECHNOLOGY GEN AI INTERN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Norfolk Southern</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Pinecone, PyTorch, spaCy, NLTK, Git, NoSQL, Matplotlib, Python</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db3ff8af5d931a12</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Engineer, Global Credit Technology</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>The Carlyle Group</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>Washington, DC, US USA</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D20" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Snowflake, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=178bc04a819dbf0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Pager Health</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f140484f5766fbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI Engineer Intern (Speech, RL, Scale AI,</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Centific Global Solutions</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Redmond, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Hadoop, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=44199a6387798252</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Associate Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ThredUp</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, OpenCV, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1377cc0d07fba26f</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Brightree</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de6f34be14e3ca39</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Peoria, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Snowflake, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e94318b1da616aa9</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Engineer III- Big Data / AI/ML / Python / React</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, TensorFlow, PyTorch, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49ea010d2003aadb</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CTI Consulting</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, CI/CD, Databricks, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3dc78df55e001f62</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior DevOps / SRE Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0aab84f6561c7f90</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior DevOps / SRE Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9dfeaa31bf45d32</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior DevOps / SRE Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ccbeec076a9a880f</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior DevOps / SRE Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f9ed0c32d69240d</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior DevOps / SRE Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a113b4e833dd3ede</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Scientist, NA</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Vantage Data Centers</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0d4733941c3a3859</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative &amp; Agentic AI Solutions: Senior Consultant</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Alvarez &amp; Marsal</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, EC2, FastAPI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e742b1374b9900f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Summer 2026 Intern - Software Engineer (Web/App Development)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Western Digital</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Snowflake, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4fa6cd3419de28e0</t>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48853dfb16fe760f</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>NVIDIA AI Infrastructure &amp; Kubernetes Platform Engineer Remote</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>IT Search Corp</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc0b0acee9ffab30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (P2408)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>84.51°</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, PySpark, Hadoop, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ecae6fe18269ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist (P2408) New</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>84.51°</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, PySpark, Hadoop, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fbc8d02b219ced5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Sr. Data Scientist – Finance Analytics, Automation &amp; AI (AAA)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>The Home Depot</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=379fe679cd4fa1ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>K2 Space</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0c8191defc50d4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Software Engineering Advisor - Evernorth</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>The Cigna Group</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, LangChain, FastAPI, Docker, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2185d4ceaa48b2b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-25.xlsx
+++ b/daily_matches/job_matches_2026-03-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior - Jacksonville</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Hugging Face, TensorFlow, PyTorch, spaCy</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e82e10477b4aafab</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd5bde56b916bab</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>WellRithms</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Athena, Redshift, Snowflake, Redshift, PySpark, MySQL</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, TensorFlow, PyTorch, Redshift, Git, Snowflake, Redshift</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=683e3c3b168935d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8f21680e47d80ce2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Service Delivery Center, AI &amp; Data, Machine Learning Engineer (MLE) - Senior</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Insight</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Manayunk, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, AWS SageMaker, AKS, Snowflake</t>
+          <t>RAG, S3, Glue, Redshift, Synapse, Kinesis, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d763612c10a5d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c469fe05779639</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>API Security Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Edison, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Keras</t>
+          <t>Copilot, S3, EC2, FastAPI, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa3c94dcb3790a71</t>
+          <t>https://www.indeed.com/viewjob?jk=7540039fe27c9ab2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, PostgreSQL, Power BI</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, MLflow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad178c68fd591147</t>
+          <t>https://www.indeed.com/viewjob?jk=b7a1b3b678b99f2a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ECG / TCU Product Development Engineer</t>
+          <t>AI DevOps and Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Crowe LLP</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, BigQuery, MLflow, CI/CD, Git, BigQuery</t>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, FAISS, Pinecone, Azure ML, EC2, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ee6848e77fa6c4</t>
+          <t>https://www.indeed.com/viewjob?jk=2828050f215fd3ad</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Air Methods</t>
+          <t>Labor Pharmacy Benefit Solutions, LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>West Jordan, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, PySpark, NoSQL, Power BI</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, S3, CI/CD, GitHub Actions, Git, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9578bd5325c490c</t>
+          <t>https://www.indeed.com/viewjob?jk=cbe4152f2d40f74f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Python Engineer</t>
+          <t>DevOps/AI Ops Administrator</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gemini, TensorFlow, PyTorch, Keras, Docker, Git, PySpark, Hadoop, MySQL, Python</t>
+          <t>Generative AI, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9ac899e2c755ad6</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ac379ca55b9cb0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Technical Support Engineer</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kevel</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, Athena, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,54 +776,54 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cea1ef2d8d9fcfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=8fc1743862b83549</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior AI/ML Software Engineer</t>
+          <t>Applied AI Scientist</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FullSteam LLC</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Hugging Face, Prompt Engineering, PyTorch, FastAPI, CI/CD, Python, R, Scala</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Hadoop, Tableau, Power BI, Matplotlib, Seaborn, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=677372de10e090b7</t>
+          <t>https://www.indeed.com/viewjob?jk=99144a4589d84498</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Fall 2026 Co-Op - Software Engineer (AI/ML)</t>
+          <t>Senior Software Engineer - AI-Enabled Systems</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cirrus Logic</t>
+          <t>Asure Software</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, Copilot, S3, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92fa3013eb9e9bf</t>
+          <t>https://www.indeed.com/viewjob?jk=b7e78ac14baf838a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI/MLOps Architect - R&amp;D IT</t>
+          <t>Full Stack AI Engineer (Healthcare Navigation)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Driscoll's</t>
+          <t>TouchCare</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Watsonville, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, Docker, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Copilot, CI/CD, Jenkins, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1e239b6621a4320</t>
+          <t>https://www.indeed.com/viewjob?jk=b361709f1d406d5b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer (GenAI)</t>
+          <t>Cognos Dashboard Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HirexHire</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Docker, Git, PostgreSQL, SQL, R, Scala</t>
+          <t>RAG, Copilot, Synapse, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80be67baadba3658</t>
+          <t>https://www.indeed.com/viewjob?jk=fbca8c5c177fee3b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Fall 2026 Co-Op - Software Engineer (AI/ML)</t>
+          <t>Cognos Dashboard Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cirrus Logic</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Git, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Synapse, FastAPI, Docker, CI/CD, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8938f2d7b1393514</t>
+          <t>https://www.indeed.com/viewjob?jk=59729c9b48128832</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Consulting - Tech Consulting - FinTech - FSO, Blockchain and AI Engineering - Senior</t>
+          <t>SAP AI Business Services Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, AKS, Terraform, Git, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, FastAPI, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aa6247258a47d06</t>
+          <t>https://www.indeed.com/viewjob?jk=fb6c18a382cdeb72</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TELUS Digital</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Docker, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,812 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5937ce7afea2561e</t>
+          <t>https://www.indeed.com/viewjob?jk=cccc36d80066799b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Real Time Product Engineering</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LSEG (London Stock Exchange Group)</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, FastAPI, Docker, Kubernetes, Git, Kafka, PostgreSQL, Python</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ffe490b5703e8ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer (junior career)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, MLflow, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77efd780b76cbcfb</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist -AI (P1966)</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>84.51°</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, LangChain, RAG, Hugging Face, Prompt Engineering, Git, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d79c3b549f59acd4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Keras, MLflow, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0ff0a3a3b4c1e56</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Engineering &amp; Integration</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Lake, Git, Snowflake, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1fa666427f4129e</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Engineering &amp; Integration</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Lake, Git, Snowflake, Databricks, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c750325324ef95ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Associate Network Security Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NC, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, BigQuery, Snowflake, Databricks, BigQuery, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1cf26dea742dfb68</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Cloud/Software Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Conagra Brands</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91fed0508199c0e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Developer - AI Software Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Neuberger Berman</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, Pinecone, Prompt Engineering, Docker, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7a63af866f0f1bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Intermediate Software Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Transamerica</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd029f900d2deee1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Cognos Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, Databricks, PySpark, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6124d6f05994ef55</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Kubernetes Security Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=baba5c1644115a60</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Resmed</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Git, Kafka, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbef80877c2d09ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Java React Developer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rubikk</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f78dca93211b726d</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Senior DevOps / SRE Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, S3, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5266edf98c28e697</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Human Resources Data Scientist</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Boeing</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Data Scientist, MLflow, CI/CD, Terraform, Tableau, Power BI, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b82a19e444d40c99</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Frontend Engineer (Angular) – Healthcare SaaS</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Davie, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, S3, CI/CD, Git, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acf3d3997cdd84b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Hilcorp Energy Company</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
         <v>10</v>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=af22d8e1fc32f436</t>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5ce13aca6e978cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Cognos Business Intelligence Analyst</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NY, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Generative AI, Databricks, PySpark, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5f0f39ab230c0b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Blockchain Data Storage</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Coinbase</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, S3, Kafka, MongoDB, R, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb39af28877d82e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Crowe LLP</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Sarasota, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, FAISS, Pinecone, Kubernetes, Terraform, R, Scala</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb87af8541cb37cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Search and Recommendations</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CarMax</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Data Scientist, Git, Databricks, Tableau, Matplotlib, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1f378a1eeedd64a</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Y2D Innovations</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Georgiana, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f8ebff9ef75b83ae</t>
         </is>
       </c>
     </row>
